--- a/docs/gantt.xlsx
+++ b/docs/gantt.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD5868D-C833-4330-B0AF-5DA73ACB2C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ECA99C8-F209-4861-9473-45200927E18A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="780" windowWidth="16425" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Гантт" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="51">
   <si>
     <t>План проекта (Гантт) · пары 5–30 · магазин обуви</t>
   </si>
@@ -164,9 +164,6 @@
   </si>
   <si>
     <t>Команда (ФИО):</t>
-  </si>
-  <si>
-    <t>в работе</t>
   </si>
   <si>
     <t>Синкевич А.А.</t>
@@ -639,7 +636,7 @@
         <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -656,7 +653,7 @@
         <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -851,12 +848,12 @@
         <v>47</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
